--- a/DataTables/DetailText/剧情/024_04王百堂来访.xlsx
+++ b/DataTables/DetailText/剧情/024_04王百堂来访.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CF5068E-1579-4212-B97C-4EA773F5082E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D221D0E-BA00-43B6-BE89-81FAF1583212}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1620" yWindow="5955" windowWidth="16050" windowHeight="8025" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story" sheetId="3" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="44">
   <si>
     <t>LineIndex</t>
   </si>
@@ -58,9 +58,6 @@
   </si>
   <si>
     <t>Text</t>
-  </si>
-  <si>
-    <t>subtitle</t>
   </si>
   <si>
     <t>left</t>
@@ -330,15 +327,11 @@
     <phoneticPr fontId="4"/>
   </si>
   <si>
-    <t>心得+5</t>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
     <t>恩公！小生拜见恩公。</t>
     <phoneticPr fontId="4"/>
   </si>
   <si>
-    <t>008_02</t>
+    <t>024_02</t>
     <phoneticPr fontId="4"/>
   </si>
 </sst>
@@ -797,78 +790,78 @@
   <sheetData>
     <row r="1" spans="1:20" s="21" customFormat="1" ht="18">
       <c r="A1" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="B1" s="17" t="s">
+      <c r="C1" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="D1" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="C1" s="18" t="s">
+      <c r="E1" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="F1" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="G1" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="H1" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="I1" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="K1" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="L1" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="M1" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="N1" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="O1" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="P1" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="D1" s="18" t="s">
-        <v>17</v>
-      </c>
-      <c r="E1" s="14" t="s">
-        <v>30</v>
-      </c>
-      <c r="F1" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="G1" s="14" t="s">
-        <v>31</v>
-      </c>
-      <c r="H1" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="I1" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="J1" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="K1" s="14" t="s">
-        <v>22</v>
-      </c>
-      <c r="L1" s="19" t="s">
-        <v>32</v>
-      </c>
-      <c r="M1" s="15" t="s">
-        <v>24</v>
-      </c>
-      <c r="N1" s="15" t="s">
-        <v>23</v>
-      </c>
-      <c r="O1" s="15" t="s">
+      <c r="Q1" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="R1" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="P1" s="15" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q1" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="R1" s="15" t="s">
-        <v>26</v>
-      </c>
       <c r="S1" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="T1" s="20" t="s">
         <v>13</v>
-      </c>
-      <c r="T1" s="20" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="2" spans="1:20" s="21" customFormat="1" ht="18">
       <c r="A2" s="22" t="s">
+        <v>36</v>
+      </c>
+      <c r="B2" s="23" t="s">
         <v>37</v>
       </c>
-      <c r="B2" s="23" t="s">
+      <c r="C2" s="23" t="s">
         <v>38</v>
       </c>
-      <c r="C2" s="23" t="s">
-        <v>39</v>
-      </c>
       <c r="D2" s="23">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E2" s="23"/>
       <c r="F2" s="23"/>
@@ -876,11 +869,11 @@
       <c r="H2" s="23"/>
       <c r="I2" s="22"/>
       <c r="J2" s="26" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K2" s="23"/>
       <c r="L2" s="23" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="M2" s="22"/>
       <c r="N2" s="23"/>
@@ -888,7 +881,7 @@
       <c r="P2" s="23"/>
       <c r="Q2" s="23"/>
       <c r="R2" s="24">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="S2" s="24" t="b">
         <v>1</v>
@@ -1172,7 +1165,7 @@
         <v>7</v>
       </c>
       <c r="I1" s="5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -1180,21 +1173,21 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E2" s="2"/>
       <c r="F2" s="7"/>
       <c r="G2" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I2" s="1"/>
     </row>
@@ -1203,19 +1196,19 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E3" s="2"/>
       <c r="F3" s="7"/>
       <c r="G3" s="2"/>
       <c r="H3" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="I3" s="1"/>
     </row>
@@ -1224,19 +1217,19 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E4" s="2"/>
       <c r="F4" s="7"/>
       <c r="G4" s="2"/>
       <c r="H4" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I4" s="1"/>
     </row>
@@ -1245,19 +1238,19 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E5" s="2"/>
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
       <c r="H5" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I5" s="1"/>
     </row>
@@ -1266,37 +1259,31 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E6" s="2"/>
       <c r="F6" s="2"/>
       <c r="G6" s="2"/>
       <c r="H6" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I6" s="1"/>
     </row>
     <row r="7" spans="1:9">
-      <c r="A7" s="3">
-        <v>6</v>
-      </c>
-      <c r="B7" s="25" t="s">
-        <v>8</v>
-      </c>
+      <c r="A7" s="3"/>
+      <c r="B7" s="25"/>
       <c r="C7" s="3"/>
       <c r="D7" s="2"/>
       <c r="E7" s="3"/>
       <c r="F7" s="3"/>
       <c r="G7" s="3"/>
-      <c r="H7" s="3" t="s">
-        <v>43</v>
-      </c>
+      <c r="H7" s="3"/>
       <c r="I7" s="3"/>
     </row>
     <row r="8" spans="1:9">
